--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_aysen_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_aysen_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:12</t>
+    <t xml:space="preserve">2026-09-29 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_aysen_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_aysen_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:08</t>
+    <t xml:space="preserve">2026-09-29 18:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -507,10 +507,10 @@
         <v>7.53</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>75.09</v>
+        <v>75.08</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>67.56</v>
+        <v>67.55</v>
       </c>
     </row>
     <row r="4">
@@ -538,7 +538,7 @@
         <v>49.77</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>57.25</v>
+        <v>57.24</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_aysen_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_aysen_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:39</t>
+    <t xml:space="preserve">2026-10-05 04:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -507,10 +507,10 @@
         <v>7.53</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>75.08</v>
+        <v>75.09</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>67.55</v>
+        <v>67.56</v>
       </c>
     </row>
     <row r="4">
@@ -535,10 +535,10 @@
         <v>-7.47</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>49.77</v>
+        <v>49.78</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>57.24</v>
+        <v>57.25</v>
       </c>
     </row>
   </sheetData>
